--- a/backend/data/financials_by_company/1JUN.MI.xlsx
+++ b/backend/data/financials_by_company/1JUN.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,56 +662,24 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-1120948</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="D2" t="n">
-        <v>912497000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-3947000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-3947000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>467553000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3664059000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>908550000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>440997000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-26431000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>37156000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>19033000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>291819052</v>
-      </c>
-      <c r="P2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4967360000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>102000000</v>
       </c>
@@ -719,140 +687,92 @@
         <v>102000000</v>
       </c>
       <c r="T2" t="n">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="U2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>288993000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>114848000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>403841000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3171000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-3171000</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>-1148000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>-26431000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>8308000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>37156000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>19033000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>424524000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1303301000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>4592000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>135742000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1167075000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>964571000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>202504000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1727825000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3664059000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5391884000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5391884000</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-678750</v>
+        <v>-452032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.224</v>
       </c>
       <c r="D3" t="n">
-        <v>886554000</v>
+        <v>766093000</v>
       </c>
       <c r="E3" t="n">
-        <v>-2715000</v>
+        <v>-2018000</v>
       </c>
       <c r="F3" t="n">
-        <v>-2715000</v>
+        <v>-2018000</v>
       </c>
       <c r="G3" t="n">
-        <v>299275000</v>
+        <v>269168000</v>
       </c>
       <c r="H3" t="n">
-        <v>446724000</v>
+        <v>400557000</v>
       </c>
       <c r="I3" t="n">
-        <v>3822355000</v>
+        <v>3290043000</v>
       </c>
       <c r="J3" t="n">
-        <v>883839000</v>
+        <v>764075000</v>
       </c>
       <c r="K3" t="n">
-        <v>437115000</v>
+        <v>363518000</v>
       </c>
       <c r="L3" t="n">
-        <v>-31487000</v>
+        <v>-16659000</v>
       </c>
       <c r="M3" t="n">
-        <v>37987000</v>
+        <v>16117000</v>
       </c>
       <c r="N3" t="n">
-        <v>11890000</v>
+        <v>3302000</v>
       </c>
       <c r="O3" t="n">
-        <v>301311250</v>
+        <v>270733968</v>
       </c>
       <c r="P3" t="n">
-        <v>299275000</v>
+        <v>269168000</v>
       </c>
       <c r="Q3" t="n">
-        <v>5124213000</v>
+        <v>4387987000</v>
       </c>
       <c r="R3" t="n">
         <v>102000000</v>
@@ -861,144 +781,144 @@
         <v>102000000</v>
       </c>
       <c r="T3" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="U3" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>299275000</v>
+        <v>269168000</v>
       </c>
       <c r="W3" t="n">
-        <v>299275000</v>
+        <v>269168000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>299275000</v>
+        <v>269168000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-407000</v>
       </c>
       <c r="AA3" t="n">
-        <v>299275000</v>
+        <v>269575000</v>
       </c>
       <c r="AB3" t="n">
-        <v>299275000</v>
+        <v>269575000</v>
       </c>
       <c r="AC3" t="n">
-        <v>99853000</v>
+        <v>77826000</v>
       </c>
       <c r="AD3" t="n">
-        <v>399128000</v>
+        <v>347401000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-7000</v>
+        <v>5773000</v>
       </c>
       <c r="AF3" t="n">
-        <v>429000</v>
+        <v>-5404000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-422000</v>
+        <v>-369000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-31487000</v>
+        <v>-16659000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5390000</v>
+        <v>3844000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>37987000</v>
+        <v>16117000</v>
       </c>
       <c r="AK3" t="n">
-        <v>11890000</v>
+        <v>3302000</v>
       </c>
       <c r="AL3" t="n">
-        <v>421674000</v>
+        <v>375307000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1301858000</v>
+        <v>1097944000</v>
       </c>
       <c r="AN3" t="n">
-        <v>9647000</v>
+        <v>652000</v>
       </c>
       <c r="AO3" t="n">
-        <v>120673000</v>
+        <v>113103000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1177815000</v>
+        <v>994124000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>975028000</v>
+        <v>833549000</v>
       </c>
       <c r="AR3" t="n">
-        <v>202787000</v>
+        <v>160575000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1723532000</v>
+        <v>1473251000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3822355000</v>
+        <v>3290043000</v>
       </c>
       <c r="AU3" t="n">
-        <v>5545887000</v>
+        <v>4763294000</v>
       </c>
       <c r="AV3" t="n">
-        <v>5545887000</v>
+        <v>4763294000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-452032</v>
+        <v>-678750</v>
       </c>
       <c r="C4" t="n">
-        <v>0.224</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>766093000</v>
+        <v>886554000</v>
       </c>
       <c r="E4" t="n">
-        <v>-2018000</v>
+        <v>-2715000</v>
       </c>
       <c r="F4" t="n">
-        <v>-2018000</v>
+        <v>-2715000</v>
       </c>
       <c r="G4" t="n">
-        <v>269168000</v>
+        <v>299275000</v>
       </c>
       <c r="H4" t="n">
-        <v>400557000</v>
+        <v>446724000</v>
       </c>
       <c r="I4" t="n">
-        <v>3290043000</v>
+        <v>3822355000</v>
       </c>
       <c r="J4" t="n">
-        <v>764075000</v>
+        <v>883839000</v>
       </c>
       <c r="K4" t="n">
-        <v>363518000</v>
+        <v>437115000</v>
       </c>
       <c r="L4" t="n">
-        <v>-16659000</v>
+        <v>-31487000</v>
       </c>
       <c r="M4" t="n">
-        <v>16117000</v>
+        <v>37987000</v>
       </c>
       <c r="N4" t="n">
-        <v>3302000</v>
+        <v>11890000</v>
       </c>
       <c r="O4" t="n">
-        <v>270733968</v>
+        <v>301311250</v>
       </c>
       <c r="P4" t="n">
-        <v>269168000</v>
+        <v>299275000</v>
       </c>
       <c r="Q4" t="n">
-        <v>4387987000</v>
+        <v>5124213000</v>
       </c>
       <c r="R4" t="n">
         <v>102000000</v>
@@ -1007,144 +927,144 @@
         <v>102000000</v>
       </c>
       <c r="T4" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="V4" t="n">
-        <v>269168000</v>
+        <v>299275000</v>
       </c>
       <c r="W4" t="n">
-        <v>269168000</v>
+        <v>299275000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>269168000</v>
+        <v>299275000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-407000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>269575000</v>
+        <v>299275000</v>
       </c>
       <c r="AB4" t="n">
-        <v>269575000</v>
+        <v>299275000</v>
       </c>
       <c r="AC4" t="n">
-        <v>77826000</v>
+        <v>99853000</v>
       </c>
       <c r="AD4" t="n">
-        <v>347401000</v>
+        <v>399128000</v>
       </c>
       <c r="AE4" t="n">
-        <v>5773000</v>
+        <v>-7000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-5404000</v>
+        <v>429000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-369000</v>
+        <v>-422000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-16659000</v>
+        <v>-31487000</v>
       </c>
       <c r="AI4" t="n">
-        <v>3844000</v>
+        <v>5390000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16117000</v>
+        <v>37987000</v>
       </c>
       <c r="AK4" t="n">
-        <v>3302000</v>
+        <v>11890000</v>
       </c>
       <c r="AL4" t="n">
-        <v>375307000</v>
+        <v>421674000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1097944000</v>
+        <v>1301858000</v>
       </c>
       <c r="AN4" t="n">
-        <v>652000</v>
+        <v>9647000</v>
       </c>
       <c r="AO4" t="n">
-        <v>113103000</v>
+        <v>120673000</v>
       </c>
       <c r="AP4" t="n">
-        <v>994124000</v>
+        <v>1177815000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>833549000</v>
+        <v>975028000</v>
       </c>
       <c r="AR4" t="n">
-        <v>160575000</v>
+        <v>202787000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1473251000</v>
+        <v>1723532000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3290043000</v>
+        <v>3822355000</v>
       </c>
       <c r="AU4" t="n">
-        <v>4763294000</v>
+        <v>5545887000</v>
       </c>
       <c r="AV4" t="n">
-        <v>4763294000</v>
+        <v>5545887000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-396864</v>
+        <v>-1961664.190193</v>
       </c>
       <c r="C5" t="n">
-        <v>0.234</v>
+        <v>0.284299</v>
       </c>
       <c r="D5" t="n">
-        <v>741203000</v>
+        <v>915500000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1696000</v>
+        <v>-6900000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1696000</v>
+        <v>-6900000</v>
       </c>
       <c r="G5" t="n">
-        <v>266248000</v>
+        <v>289000000</v>
       </c>
       <c r="H5" t="n">
-        <v>377026000</v>
+        <v>467600000</v>
       </c>
       <c r="I5" t="n">
-        <v>2916378000</v>
+        <v>3664100000</v>
       </c>
       <c r="J5" t="n">
-        <v>739507000</v>
+        <v>908600000</v>
       </c>
       <c r="K5" t="n">
-        <v>362481000</v>
+        <v>441000000</v>
       </c>
       <c r="L5" t="n">
-        <v>-13341000</v>
+        <v>-26500000</v>
       </c>
       <c r="M5" t="n">
-        <v>13348000</v>
+        <v>37200000</v>
       </c>
       <c r="N5" t="n">
-        <v>1230000</v>
+        <v>19000000</v>
       </c>
       <c r="O5" t="n">
-        <v>267547136</v>
+        <v>293938335.809807</v>
       </c>
       <c r="P5" t="n">
-        <v>266248000</v>
+        <v>289000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3883285000</v>
+        <v>4964400000</v>
       </c>
       <c r="R5" t="n">
         <v>102000000</v>
@@ -1153,89 +1073,221 @@
         <v>102000000</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="V5" t="n">
-        <v>266248000</v>
+        <v>289000000</v>
       </c>
       <c r="W5" t="n">
-        <v>266248000</v>
+        <v>289000000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>266248000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-1148000</v>
-      </c>
+        <v>289000000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>267396000</v>
+        <v>289000000</v>
       </c>
       <c r="AB5" t="n">
-        <v>267396000</v>
+        <v>289000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>81737000</v>
+        <v>114800000</v>
       </c>
       <c r="AD5" t="n">
-        <v>349133000</v>
+        <v>403800000</v>
       </c>
       <c r="AE5" t="n">
-        <v>276000</v>
+        <v>200000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-276000</v>
+        <v>-200000</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-13341000</v>
+        <v>-26500000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1223000</v>
+        <v>8300000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13348000</v>
+        <v>37200000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1230000</v>
+        <v>19000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>356530000</v>
+        <v>427500000</v>
       </c>
       <c r="AM5" t="n">
-        <v>966907000</v>
+        <v>1300300000</v>
       </c>
       <c r="AN5" t="n">
-        <v>814000</v>
+        <v>1600000</v>
       </c>
       <c r="AO5" t="n">
-        <v>95381000</v>
+        <v>135700000</v>
       </c>
       <c r="AP5" t="n">
-        <v>876226000</v>
+        <v>1167100000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>740691000</v>
+        <v>964600000</v>
       </c>
       <c r="AR5" t="n">
-        <v>135535000</v>
+        <v>202500000</v>
       </c>
       <c r="AS5" t="n">
-        <v>1323437000</v>
+        <v>1727800000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2916378000</v>
+        <v>3664100000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4239815000</v>
+        <v>5391900000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4239815000</v>
+        <v>5391900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-18195000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>835700000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-121300000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-121300000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>478000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3732400000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>714400000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>236400000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-29200000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>16200000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>206705000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5160700000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>92800000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>196400000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-115900000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>115900000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>-29200000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16200000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>341300000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1428300000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>163400000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1267100000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1026100000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>241000000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1769600000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3732400000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>5502100000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5502100000</v>
       </c>
     </row>
   </sheetData>
@@ -1249,7 +1301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ5"/>
+  <dimension ref="A1:CD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,234 +1690,126 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>Assets Held For Sale Current</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>102000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>696129000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1794403000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2875374000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>923717000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1794403000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>257057000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2436302000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2734161000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2436302000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>2436302000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2364988000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>78385000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>102000000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4692058000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2541852000</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1306000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>797000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2892000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>179356000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>19788000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>72585000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>485549000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>187690000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>297859000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>98008000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2150206000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>116027000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>210580000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>69367000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>141213000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>322744000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>620173000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>30081000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>590092000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7128360000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4054437000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12187000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>126622000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2831000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>509000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>509000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>78870000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>78870000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>641899000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>251494000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>390405000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1830590000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-1860082000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3690672000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>31587000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2238204000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>534847000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>886034000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>3073923000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>4820000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>8918000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>58628000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>822214000</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="n">
-        <v>436295000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>60836000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>325083000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>141234000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>23615000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>857329000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>694473000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>169617000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>524856000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>524856000</v>
-      </c>
+        <v>32074000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>10745000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>6373000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>91792000</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
       <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>102000000</v>
@@ -1874,43 +1818,43 @@
         <v>102000000</v>
       </c>
       <c r="D3" t="n">
-        <v>186173000</v>
+        <v>80218000</v>
       </c>
       <c r="E3" t="n">
-        <v>938390000</v>
+        <v>624918000</v>
       </c>
       <c r="F3" t="n">
-        <v>1615847000</v>
+        <v>1835584000</v>
       </c>
       <c r="G3" t="n">
-        <v>2910562000</v>
+        <v>2459057000</v>
       </c>
       <c r="H3" t="n">
-        <v>626881000</v>
+        <v>929693000</v>
       </c>
       <c r="I3" t="n">
-        <v>1615847000</v>
+        <v>1835584000</v>
       </c>
       <c r="J3" t="n">
-        <v>250085000</v>
+        <v>217313000</v>
       </c>
       <c r="K3" t="n">
-        <v>2222257000</v>
+        <v>2051452000</v>
       </c>
       <c r="L3" t="n">
-        <v>2404804000</v>
+        <v>2324559000</v>
       </c>
       <c r="M3" t="n">
-        <v>2222257000</v>
+        <v>2051452000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2222257000</v>
+        <v>2051452000</v>
       </c>
       <c r="P3" t="n">
-        <v>2151415000</v>
+        <v>1920420000</v>
       </c>
       <c r="Q3" t="n">
         <v>78385000</v>
@@ -1922,180 +1866,184 @@
         <v>102000000</v>
       </c>
       <c r="T3" t="n">
-        <v>4687600000</v>
+        <v>4112671000</v>
       </c>
       <c r="U3" t="n">
-        <v>2236155000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>810000</v>
-      </c>
+        <v>2129757000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>2555000</v>
+        <v>331000</v>
       </c>
       <c r="X3" t="n">
-        <v>180428000</v>
+        <v>158900000</v>
       </c>
       <c r="Y3" t="n">
-        <v>19297000</v>
+        <v>23096000</v>
       </c>
       <c r="Z3" t="n">
-        <v>57070000</v>
+        <v>43895000</v>
       </c>
       <c r="AA3" t="n">
-        <v>366218000</v>
+        <v>429429000</v>
       </c>
       <c r="AB3" t="n">
-        <v>183671000</v>
+        <v>156322000</v>
       </c>
       <c r="AC3" t="n">
-        <v>182547000</v>
+        <v>273107000</v>
       </c>
       <c r="AD3" t="n">
-        <v>89993000</v>
+        <v>66632000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2451445000</v>
+        <v>1982914000</v>
       </c>
       <c r="AF3" t="n">
-        <v>128453000</v>
+        <v>115067000</v>
       </c>
       <c r="AG3" t="n">
-        <v>572172000</v>
+        <v>195489000</v>
       </c>
       <c r="AH3" t="n">
-        <v>66414000</v>
+        <v>60991000</v>
       </c>
       <c r="AI3" t="n">
-        <v>505758000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>134498000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>12585000</v>
+      </c>
       <c r="AK3" t="n">
-        <v>342796000</v>
+        <v>291705000</v>
       </c>
       <c r="AL3" t="n">
-        <v>581734000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>574228000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1052000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>21642000</v>
+        <v>18032000</v>
       </c>
       <c r="AO3" t="n">
-        <v>560092000</v>
+        <v>556196000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6909857000</v>
+        <v>6164123000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3831531000</v>
+        <v>3251516000</v>
       </c>
       <c r="AR3" t="n">
-        <v>10091000</v>
+        <v>17487000</v>
       </c>
       <c r="AS3" t="n">
-        <v>120310000</v>
+        <v>107621000</v>
       </c>
       <c r="AT3" t="n">
-        <v>6931000</v>
+        <v>15881000</v>
       </c>
       <c r="AU3" t="n">
-        <v>10298000</v>
+        <v>29005000</v>
       </c>
       <c r="AV3" t="n">
-        <v>10298000</v>
+        <v>29005000</v>
       </c>
       <c r="AW3" t="n">
-        <v>70459000</v>
+        <v>70452000</v>
       </c>
       <c r="AX3" t="n">
-        <v>70459000</v>
+        <v>70452000</v>
       </c>
       <c r="AY3" t="n">
-        <v>606410000</v>
+        <v>215868000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>233680000</v>
+        <v>133043000</v>
       </c>
       <c r="BA3" t="n">
-        <v>372730000</v>
+        <v>82825000</v>
       </c>
       <c r="BB3" t="n">
-        <v>1786306000</v>
+        <v>1729001000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-1802121000</v>
+        <v>-1686297000</v>
       </c>
       <c r="BD3" t="n">
-        <v>3588427000</v>
+        <v>3415298000</v>
       </c>
       <c r="BE3" t="n">
-        <v>19109000</v>
+        <v>19968000</v>
       </c>
       <c r="BF3" t="n">
-        <v>2180486000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>536562000</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>852270000</v>
-      </c>
+        <v>2590655000</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>804675000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3078326000</v>
+        <v>2912607000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6921000</v>
+        <v>7093000</v>
       </c>
       <c r="BL3" t="n">
-        <v>9051000</v>
+        <v>9338000</v>
       </c>
       <c r="BM3" t="n">
-        <v>32587000</v>
+        <v>37262000</v>
       </c>
       <c r="BN3" t="n">
-        <v>894021000</v>
-      </c>
-      <c r="BO3" t="inlineStr"/>
+        <v>956734000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>100140000</v>
+      </c>
       <c r="BP3" t="n">
-        <v>437119000</v>
+        <v>469797000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>79225000</v>
+        <v>86204000</v>
       </c>
       <c r="BR3" t="n">
-        <v>377677000</v>
+        <v>400733000</v>
       </c>
       <c r="BS3" t="n">
-        <v>137655000</v>
+        <v>84831000</v>
       </c>
       <c r="BT3" t="n">
-        <v>10606000</v>
+        <v>16074000</v>
       </c>
       <c r="BU3" t="n">
-        <v>905071000</v>
+        <v>898624000</v>
       </c>
       <c r="BV3" t="n">
-        <v>642568000</v>
+        <v>496448000</v>
       </c>
       <c r="BW3" t="n">
-        <v>140436000</v>
+        <v>169061000</v>
       </c>
       <c r="BX3" t="n">
-        <v>502132000</v>
+        <v>327387000</v>
       </c>
       <c r="BY3" t="n">
-        <v>502132000</v>
+        <v>320573000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>11886000</v>
-      </c>
+        <v>6814000</v>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>102000000</v>
@@ -2104,43 +2052,43 @@
         <v>102000000</v>
       </c>
       <c r="D4" t="n">
-        <v>80218000</v>
+        <v>186173000</v>
       </c>
       <c r="E4" t="n">
-        <v>624918000</v>
+        <v>938390000</v>
       </c>
       <c r="F4" t="n">
-        <v>1835584000</v>
+        <v>1615847000</v>
       </c>
       <c r="G4" t="n">
-        <v>2459057000</v>
+        <v>2910562000</v>
       </c>
       <c r="H4" t="n">
-        <v>929693000</v>
+        <v>626881000</v>
       </c>
       <c r="I4" t="n">
-        <v>1835584000</v>
+        <v>1615847000</v>
       </c>
       <c r="J4" t="n">
-        <v>217313000</v>
+        <v>250085000</v>
       </c>
       <c r="K4" t="n">
-        <v>2051452000</v>
+        <v>2222257000</v>
       </c>
       <c r="L4" t="n">
-        <v>2324559000</v>
+        <v>2404804000</v>
       </c>
       <c r="M4" t="n">
-        <v>2051452000</v>
+        <v>2222257000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2051452000</v>
+        <v>2222257000</v>
       </c>
       <c r="P4" t="n">
-        <v>1920420000</v>
+        <v>2151415000</v>
       </c>
       <c r="Q4" t="n">
         <v>78385000</v>
@@ -2152,180 +2100,184 @@
         <v>102000000</v>
       </c>
       <c r="T4" t="n">
-        <v>4112671000</v>
+        <v>4687600000</v>
       </c>
       <c r="U4" t="n">
-        <v>2129757000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>2236155000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>810000</v>
+      </c>
       <c r="W4" t="n">
-        <v>331000</v>
+        <v>2555000</v>
       </c>
       <c r="X4" t="n">
-        <v>158900000</v>
+        <v>180428000</v>
       </c>
       <c r="Y4" t="n">
-        <v>23096000</v>
+        <v>19297000</v>
       </c>
       <c r="Z4" t="n">
-        <v>43895000</v>
+        <v>57070000</v>
       </c>
       <c r="AA4" t="n">
-        <v>429429000</v>
+        <v>366218000</v>
       </c>
       <c r="AB4" t="n">
-        <v>156322000</v>
+        <v>183671000</v>
       </c>
       <c r="AC4" t="n">
-        <v>273107000</v>
+        <v>182547000</v>
       </c>
       <c r="AD4" t="n">
-        <v>66632000</v>
+        <v>89993000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1982914000</v>
+        <v>2451445000</v>
       </c>
       <c r="AF4" t="n">
-        <v>115067000</v>
+        <v>128453000</v>
       </c>
       <c r="AG4" t="n">
-        <v>195489000</v>
+        <v>572172000</v>
       </c>
       <c r="AH4" t="n">
-        <v>60991000</v>
+        <v>66414000</v>
       </c>
       <c r="AI4" t="n">
-        <v>134498000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>12585000</v>
-      </c>
+        <v>505758000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>291705000</v>
+        <v>342796000</v>
       </c>
       <c r="AL4" t="n">
-        <v>574228000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1052000</v>
-      </c>
+        <v>581734000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>18032000</v>
+        <v>21642000</v>
       </c>
       <c r="AO4" t="n">
-        <v>556196000</v>
+        <v>560092000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6164123000</v>
+        <v>6909857000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3251516000</v>
+        <v>3831531000</v>
       </c>
       <c r="AR4" t="n">
-        <v>17487000</v>
+        <v>10091000</v>
       </c>
       <c r="AS4" t="n">
-        <v>107621000</v>
+        <v>120310000</v>
       </c>
       <c r="AT4" t="n">
-        <v>15881000</v>
+        <v>6931000</v>
       </c>
       <c r="AU4" t="n">
-        <v>29005000</v>
+        <v>10298000</v>
       </c>
       <c r="AV4" t="n">
-        <v>29005000</v>
+        <v>10298000</v>
       </c>
       <c r="AW4" t="n">
-        <v>70452000</v>
+        <v>70459000</v>
       </c>
       <c r="AX4" t="n">
-        <v>70452000</v>
+        <v>70459000</v>
       </c>
       <c r="AY4" t="n">
-        <v>215868000</v>
+        <v>606410000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>133043000</v>
+        <v>233680000</v>
       </c>
       <c r="BA4" t="n">
-        <v>82825000</v>
+        <v>372730000</v>
       </c>
       <c r="BB4" t="n">
-        <v>1729001000</v>
+        <v>1786306000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-1686297000</v>
+        <v>-1802121000</v>
       </c>
       <c r="BD4" t="n">
-        <v>3415298000</v>
+        <v>3588427000</v>
       </c>
       <c r="BE4" t="n">
-        <v>19968000</v>
+        <v>19109000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2590655000</v>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+        <v>2180486000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>536562000</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>852270000</v>
+      </c>
       <c r="BI4" t="n">
-        <v>804675000</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>2912607000</v>
+        <v>3078326000</v>
       </c>
       <c r="BK4" t="n">
-        <v>7093000</v>
+        <v>6921000</v>
       </c>
       <c r="BL4" t="n">
-        <v>9338000</v>
+        <v>9051000</v>
       </c>
       <c r="BM4" t="n">
-        <v>37262000</v>
+        <v>32587000</v>
       </c>
       <c r="BN4" t="n">
-        <v>956734000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>100140000</v>
-      </c>
+        <v>894021000</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="n">
-        <v>469797000</v>
+        <v>437119000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>86204000</v>
+        <v>79225000</v>
       </c>
       <c r="BR4" t="n">
-        <v>400733000</v>
+        <v>377677000</v>
       </c>
       <c r="BS4" t="n">
-        <v>84831000</v>
+        <v>137655000</v>
       </c>
       <c r="BT4" t="n">
-        <v>16074000</v>
+        <v>10606000</v>
       </c>
       <c r="BU4" t="n">
-        <v>898624000</v>
+        <v>905071000</v>
       </c>
       <c r="BV4" t="n">
-        <v>496448000</v>
+        <v>642568000</v>
       </c>
       <c r="BW4" t="n">
-        <v>169061000</v>
+        <v>140436000</v>
       </c>
       <c r="BX4" t="n">
-        <v>327387000</v>
+        <v>502132000</v>
       </c>
       <c r="BY4" t="n">
-        <v>320573000</v>
+        <v>502132000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>6814000</v>
-      </c>
+        <v>11886000</v>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>102000000</v>
@@ -2335,43 +2287,41 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>549363000</v>
+        <v>695900000</v>
       </c>
       <c r="F5" t="n">
-        <v>1599591000</v>
+        <v>1794400000</v>
       </c>
       <c r="G5" t="n">
-        <v>2067152000</v>
+        <v>2875300000</v>
       </c>
       <c r="H5" t="n">
-        <v>705684000</v>
+        <v>923800000</v>
       </c>
       <c r="I5" t="n">
-        <v>1599591000</v>
+        <v>1794400000</v>
       </c>
       <c r="J5" t="n">
-        <v>283514000</v>
+        <v>256900000</v>
       </c>
       <c r="K5" t="n">
-        <v>1801303000</v>
+        <v>2436300000</v>
       </c>
       <c r="L5" t="n">
-        <v>1940682000</v>
+        <v>2734100000</v>
       </c>
       <c r="M5" t="n">
-        <v>1802609000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1306000</v>
-      </c>
+        <v>2436300000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1801303000</v>
+        <v>2436300000</v>
       </c>
       <c r="P5" t="n">
-        <v>1719532000</v>
+        <v>2365000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>78385000</v>
+        <v>78400000</v>
       </c>
       <c r="R5" t="n">
         <v>102000000</v>
@@ -2380,177 +2330,425 @@
         <v>102000000</v>
       </c>
       <c r="T5" t="n">
-        <v>3966527000</v>
+        <v>4692100000</v>
       </c>
       <c r="U5" t="n">
-        <v>1981733000</v>
+        <v>2541900000</v>
       </c>
       <c r="V5" t="n">
-        <v>32074000</v>
+        <v>900000</v>
       </c>
       <c r="W5" t="n">
-        <v>826000</v>
+        <v>2900000</v>
       </c>
       <c r="X5" t="n">
-        <v>227796000</v>
+        <v>179400000</v>
       </c>
       <c r="Y5" t="n">
-        <v>32074000</v>
+        <v>19800000</v>
       </c>
       <c r="Z5" t="n">
-        <v>28893000</v>
+        <v>72600000</v>
       </c>
       <c r="AA5" t="n">
-        <v>293774000</v>
+        <v>485400000</v>
       </c>
       <c r="AB5" t="n">
-        <v>154395000</v>
+        <v>187600000</v>
       </c>
       <c r="AC5" t="n">
-        <v>139379000</v>
+        <v>297800000</v>
       </c>
       <c r="AD5" t="n">
-        <v>65355000</v>
+        <v>98000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1984794000</v>
+        <v>2150200000</v>
       </c>
       <c r="AF5" t="n">
-        <v>13664000</v>
+        <v>116100000</v>
       </c>
       <c r="AG5" t="n">
-        <v>255589000</v>
+        <v>210500000</v>
       </c>
       <c r="AH5" t="n">
-        <v>129119000</v>
+        <v>69300000</v>
       </c>
       <c r="AI5" t="n">
-        <v>126470000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>10745000</v>
-      </c>
+        <v>141200000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>286863000</v>
+        <v>322800000</v>
       </c>
       <c r="AL5" t="n">
-        <v>638990000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>6373000</v>
-      </c>
+        <v>620200000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>99648000</v>
+        <v>30100000</v>
       </c>
       <c r="AO5" t="n">
-        <v>532969000</v>
+        <v>590100000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5769136000</v>
+        <v>7128400000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3078658000</v>
+        <v>4054400000</v>
       </c>
       <c r="AR5" t="n">
-        <v>33753000</v>
+        <v>12300000</v>
       </c>
       <c r="AS5" t="n">
-        <v>121915000</v>
+        <v>126600000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1245000</v>
+        <v>2800000</v>
       </c>
       <c r="AU5" t="n">
-        <v>45278000</v>
+        <v>500000</v>
       </c>
       <c r="AV5" t="n">
-        <v>45278000</v>
+        <v>500000</v>
       </c>
       <c r="AW5" t="n">
-        <v>45696000</v>
+        <v>78900000</v>
       </c>
       <c r="AX5" t="n">
-        <v>45696000</v>
+        <v>78900000</v>
       </c>
       <c r="AY5" t="n">
-        <v>201712000</v>
+        <v>641900000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>118183000</v>
+        <v>251500000</v>
       </c>
       <c r="BA5" t="n">
-        <v>83529000</v>
+        <v>390400000</v>
       </c>
       <c r="BB5" t="n">
-        <v>1583368000</v>
+        <v>1830500000</v>
       </c>
       <c r="BC5" t="n">
-        <v>-1556633000</v>
+        <v>-1860100000</v>
       </c>
       <c r="BD5" t="n">
-        <v>3140001000</v>
+        <v>3690600000</v>
       </c>
       <c r="BE5" t="n">
-        <v>18451000</v>
+        <v>31600000</v>
       </c>
       <c r="BF5" t="n">
-        <v>2335698000</v>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+        <v>2238200000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>534800000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>886000000</v>
+      </c>
       <c r="BI5" t="n">
-        <v>785852000</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2690478000</v>
+        <v>3074000000</v>
       </c>
       <c r="BK5" t="n">
-        <v>3385000</v>
+        <v>4900000</v>
       </c>
       <c r="BL5" t="n">
-        <v>9354000</v>
+        <v>8900000</v>
       </c>
       <c r="BM5" t="n">
-        <v>20748000</v>
+        <v>58600000</v>
       </c>
       <c r="BN5" t="n">
-        <v>743105000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>91792000</v>
-      </c>
+        <v>822200000</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>353378000</v>
+        <v>436300000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>71197000</v>
+        <v>60800000</v>
       </c>
       <c r="BR5" t="n">
-        <v>318530000</v>
+        <v>325100000</v>
       </c>
       <c r="BS5" t="n">
-        <v>71314000</v>
+        <v>141300000</v>
       </c>
       <c r="BT5" t="n">
-        <v>5343000</v>
+        <v>23600000</v>
       </c>
       <c r="BU5" t="n">
-        <v>755052000</v>
+        <v>866200000</v>
       </c>
       <c r="BV5" t="n">
-        <v>710839000</v>
+        <v>694500000</v>
       </c>
       <c r="BW5" t="n">
-        <v>245574000</v>
+        <v>169600000</v>
       </c>
       <c r="BX5" t="n">
-        <v>465265000</v>
+        <v>524900000</v>
       </c>
       <c r="BY5" t="n">
-        <v>456883000</v>
+        <v>520300000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>8382000</v>
+        <v>4600000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-8900000</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-20600000</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>886800000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>691300000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1816900000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2899500000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>902200000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1816900000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>247200000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2455400000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2752300000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2455400000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>2455400000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2388100000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>78400000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>102000000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4973400000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2632200000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>164500000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14900000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>469700000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>172800000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>296900000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2341200000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>126300000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>221600000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>74400000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>147200000</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>404500000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>613900000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>25400000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>588500000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>7428800000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4185500000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>24900000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>114400000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>84900000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>84900000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>638500000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>261500000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>377000000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1826200000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-1934500000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3760700000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>36200000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2246300000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>562700000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>915500000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>3243400000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>9700000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>798200000</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>431600000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>62300000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>304300000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>876100000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>826500000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>194500000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>632000000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>626900000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-8400000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>40200000</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-19300000</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>895400000</v>
       </c>
     </row>
   </sheetData>
@@ -2564,7 +2762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2778,519 +2976,602 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Net Other Financing Charges</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Net Other Investing Changes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>439532000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-91786000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>153820000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-138426000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>524856000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>478632000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-4707000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>50931000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-386486000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-75420000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-243390000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-305424000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>62034000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-91786000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>153820000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-140541000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6041000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>106315000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-100274000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-6416000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-6416000</v>
-      </c>
+        <v>-89458000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-136192000</v>
+        <v>-77548000</v>
       </c>
       <c r="X2" t="n">
-        <v>2234000</v>
+        <v>11910000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-138426000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>577958000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-106832000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13131000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-30481000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3976000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>142803000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>196091000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>11465000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>28737000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>37564000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-131054000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-299821000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-13042000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>114848000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>467553000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>467553000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3021000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>288993000</v>
-      </c>
+        <v>-89458000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>337749000</v>
+        <v>-239464000</v>
       </c>
       <c r="C3" t="n">
-        <v>-315725000</v>
+        <v>-95551000</v>
       </c>
       <c r="D3" t="n">
-        <v>223775000</v>
+        <v>214214000</v>
       </c>
       <c r="E3" t="n">
-        <v>-134580000</v>
+        <v>-103371000</v>
       </c>
       <c r="F3" t="n">
-        <v>478632000</v>
+        <v>327357000</v>
       </c>
       <c r="G3" t="n">
-        <v>327357000</v>
+        <v>350265000</v>
       </c>
       <c r="H3" t="n">
-        <v>-7699000</v>
+        <v>-2720000</v>
       </c>
       <c r="I3" t="n">
-        <v>158974000</v>
+        <v>-20188000</v>
       </c>
       <c r="J3" t="n">
-        <v>117111000</v>
+        <v>36736000</v>
       </c>
       <c r="K3" t="n">
         <v>-68280000</v>
       </c>
       <c r="L3" t="n">
-        <v>247040000</v>
+        <v>161399000</v>
       </c>
       <c r="M3" t="n">
-        <v>338990000</v>
+        <v>42736000</v>
       </c>
       <c r="N3" t="n">
-        <v>-91950000</v>
+        <v>118663000</v>
       </c>
       <c r="O3" t="n">
-        <v>-315725000</v>
+        <v>-95551000</v>
       </c>
       <c r="P3" t="n">
-        <v>223775000</v>
+        <v>214214000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-430466000</v>
+        <v>79169000</v>
       </c>
       <c r="R3" t="n">
-        <v>26878000</v>
+        <v>182035000</v>
       </c>
       <c r="S3" t="n">
-        <v>137069000</v>
+        <v>264564000</v>
       </c>
       <c r="T3" t="n">
-        <v>-110191000</v>
+        <v>-82529000</v>
       </c>
       <c r="U3" t="n">
-        <v>-329708000</v>
+        <v>-7582000</v>
       </c>
       <c r="V3" t="n">
-        <v>-329708000</v>
+        <v>-7582000</v>
       </c>
       <c r="W3" t="n">
-        <v>-129919000</v>
+        <v>-94768000</v>
       </c>
       <c r="X3" t="n">
-        <v>4661000</v>
+        <v>8603000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-134580000</v>
+        <v>-103371000</v>
       </c>
       <c r="Z3" t="n">
-        <v>472329000</v>
+        <v>-136093000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-103777000</v>
+        <v>-81890000</v>
       </c>
       <c r="AB3" t="n">
-        <v>4648000</v>
+        <v>1848000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-30778000</v>
+        <v>-14246000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3343000</v>
+        <v>2102000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-56937000</v>
+        <v>-347226000</v>
       </c>
       <c r="AF3" t="n">
-        <v>100493000</v>
+        <v>76586000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4894000</v>
+        <v>4016000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-9567000</v>
+        <v>34455000</v>
       </c>
       <c r="AI3" t="n">
-        <v>79068000</v>
+        <v>-256873000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-222037000</v>
+        <v>-205410000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-275017000</v>
+        <v>-367586000</v>
       </c>
       <c r="AL3" t="n">
-        <v>92446000</v>
+        <v>-61321000</v>
       </c>
       <c r="AM3" t="n">
-        <v>99853000</v>
+        <v>77826000</v>
       </c>
       <c r="AN3" t="n">
-        <v>446724000</v>
+        <v>400557000</v>
       </c>
       <c r="AO3" t="n">
-        <v>446724000</v>
+        <v>400557000</v>
       </c>
       <c r="AP3" t="n">
-        <v>429000</v>
+        <v>-10068000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>299275000</v>
-      </c>
+        <v>269575000</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-239464000</v>
+        <v>337749000</v>
       </c>
       <c r="C4" t="n">
-        <v>-95551000</v>
+        <v>-315725000</v>
       </c>
       <c r="D4" t="n">
-        <v>214214000</v>
+        <v>223775000</v>
       </c>
       <c r="E4" t="n">
-        <v>-103371000</v>
+        <v>-134580000</v>
       </c>
       <c r="F4" t="n">
+        <v>478632000</v>
+      </c>
+      <c r="G4" t="n">
         <v>327357000</v>
       </c>
-      <c r="G4" t="n">
-        <v>350265000</v>
-      </c>
       <c r="H4" t="n">
-        <v>-2720000</v>
+        <v>-7699000</v>
       </c>
       <c r="I4" t="n">
-        <v>-20188000</v>
+        <v>158974000</v>
       </c>
       <c r="J4" t="n">
-        <v>36736000</v>
+        <v>117111000</v>
       </c>
       <c r="K4" t="n">
         <v>-68280000</v>
       </c>
       <c r="L4" t="n">
-        <v>161399000</v>
+        <v>247040000</v>
       </c>
       <c r="M4" t="n">
-        <v>42736000</v>
+        <v>338990000</v>
       </c>
       <c r="N4" t="n">
-        <v>118663000</v>
+        <v>-91950000</v>
       </c>
       <c r="O4" t="n">
-        <v>-95551000</v>
+        <v>-315725000</v>
       </c>
       <c r="P4" t="n">
-        <v>214214000</v>
+        <v>223775000</v>
       </c>
       <c r="Q4" t="n">
-        <v>79169000</v>
+        <v>-430466000</v>
       </c>
       <c r="R4" t="n">
-        <v>182035000</v>
+        <v>26878000</v>
       </c>
       <c r="S4" t="n">
-        <v>264564000</v>
+        <v>137069000</v>
       </c>
       <c r="T4" t="n">
-        <v>-82529000</v>
+        <v>-110191000</v>
       </c>
       <c r="U4" t="n">
-        <v>-7582000</v>
+        <v>-329708000</v>
       </c>
       <c r="V4" t="n">
-        <v>-7582000</v>
+        <v>-329708000</v>
       </c>
       <c r="W4" t="n">
-        <v>-94768000</v>
+        <v>-129919000</v>
       </c>
       <c r="X4" t="n">
-        <v>8603000</v>
+        <v>4661000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-103371000</v>
+        <v>-134580000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-136093000</v>
+        <v>472329000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-81890000</v>
+        <v>-103777000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1848000</v>
+        <v>4648000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14246000</v>
+        <v>-30778000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2102000</v>
+        <v>3343000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-347226000</v>
+        <v>-56937000</v>
       </c>
       <c r="AF4" t="n">
-        <v>76586000</v>
+        <v>100493000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4016000</v>
+        <v>-4894000</v>
       </c>
       <c r="AH4" t="n">
-        <v>34455000</v>
+        <v>-9567000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-256873000</v>
+        <v>79068000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-205410000</v>
+        <v>-222037000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-367586000</v>
+        <v>-275017000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-61321000</v>
+        <v>92446000</v>
       </c>
       <c r="AM4" t="n">
-        <v>77826000</v>
+        <v>99853000</v>
       </c>
       <c r="AN4" t="n">
-        <v>400557000</v>
+        <v>446724000</v>
       </c>
       <c r="AO4" t="n">
-        <v>400557000</v>
+        <v>446724000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-10068000</v>
+        <v>429000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>269575000</v>
-      </c>
+        <v>299275000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>161324000</v>
+        <v>578000000</v>
       </c>
       <c r="C5" t="n">
-        <v>-198401000</v>
+        <v>-91800000</v>
       </c>
       <c r="D5" t="n">
-        <v>5572000</v>
+        <v>153800000</v>
       </c>
       <c r="E5" t="n">
-        <v>-89458000</v>
+        <v>-138426000</v>
       </c>
       <c r="F5" t="n">
-        <v>350265000</v>
+        <v>524900000</v>
       </c>
       <c r="G5" t="n">
-        <v>527027000</v>
+        <v>478600000</v>
       </c>
       <c r="H5" t="n">
-        <v>8222000</v>
+        <v>-4700000</v>
       </c>
       <c r="I5" t="n">
-        <v>-184984000</v>
+        <v>51000000</v>
       </c>
       <c r="J5" t="n">
-        <v>-321960000</v>
+        <v>-386500000</v>
       </c>
       <c r="K5" t="n">
-        <v>-42780000</v>
+        <v>-75400000</v>
       </c>
       <c r="L5" t="n">
-        <v>-225873000</v>
+        <v>-243400000</v>
       </c>
       <c r="M5" t="n">
-        <v>-33044000</v>
+        <v>-305400000</v>
       </c>
       <c r="N5" t="n">
-        <v>-192829000</v>
+        <v>62000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-198401000</v>
+        <v>-91800000</v>
       </c>
       <c r="P5" t="n">
-        <v>5572000</v>
+        <v>153800000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-113806000</v>
+        <v>-140500000</v>
       </c>
       <c r="R5" t="n">
-        <v>47720000</v>
+        <v>6000000</v>
       </c>
       <c r="S5" t="n">
-        <v>514285000</v>
+        <v>106300000</v>
       </c>
       <c r="T5" t="n">
-        <v>-466565000</v>
+        <v>-100300000</v>
       </c>
       <c r="U5" t="n">
-        <v>-74501000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-74501000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-77548000</v>
+        <v>-136192000</v>
       </c>
       <c r="X5" t="n">
-        <v>11910000</v>
+        <v>2234000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-89458000</v>
+        <v>-138426000</v>
       </c>
       <c r="Z5" t="n">
-        <v>250782000</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>578000000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-106800000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>13100000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-30500000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4000000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-129920000</v>
+        <v>143000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>47584000</v>
+        <v>196200000</v>
       </c>
       <c r="AG5" t="n">
-        <v>43166000</v>
+        <v>11500000</v>
       </c>
       <c r="AH5" t="n">
-        <v>143564000</v>
+        <v>28700000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-220367000</v>
+        <v>37600000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-143867000</v>
+        <v>-131000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-284301000</v>
+        <v>-299800000</v>
       </c>
       <c r="AL5" t="n">
-        <v>21798000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
+        <v>-13000000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>114800000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>377026000</v>
+        <v>467600000</v>
       </c>
       <c r="AO5" t="n">
-        <v>377026000</v>
+        <v>467600000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-276000</v>
+        <v>3000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>267396000</v>
+        <v>289000000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-142500000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>490300000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-38800000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50900000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>633300000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>524900000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-9400000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>117800000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-144800000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-80500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-2100000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>12100000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-38800000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>50900000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-227700000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-51100000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>110900000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-162000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-18200000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-18200000</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>490300000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-72700000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-33200000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>251300000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-10900000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-198500000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-212500000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>92800000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>478000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>478000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>19100000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>103600000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-152200000</v>
       </c>
     </row>
   </sheetData>
@@ -3780,167 +4061,167 @@
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="DX1" t="inlineStr">
@@ -4043,7 +4324,7 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>25.94</v>
+        <v>24.2</v>
       </c>
       <c r="V2" t="n">
         <v>24.66</v>
@@ -4055,7 +4336,7 @@
         <v>25.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.94</v>
+        <v>24.2</v>
       </c>
       <c r="Z2" t="n">
         <v>24.66</v>
@@ -4076,13 +4357,13 @@
         <v>1779235200</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2878</v>
+        <v>0.7921</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.73</v>
+        <v>1.735</v>
       </c>
       <c r="AH2" t="n">
-        <v>8.964029</v>
+        <v>23.544556</v>
       </c>
       <c r="AI2" t="n">
         <v>128</v>
@@ -4094,19 +4375,19 @@
         <v>6</v>
       </c>
       <c r="AL2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="AP2" t="n">
-        <v>2458200000</v>
+        <v>2456160000</v>
       </c>
       <c r="AQ2" t="n">
         <v>23.98</v>
@@ -4121,10 +4402,10 @@
         <v>23.98</v>
       </c>
       <c r="AU2" t="n">
-        <v>29.3716</v>
+        <v>27.4452</v>
       </c>
       <c r="AV2" t="n">
-        <v>31.616</v>
+        <v>31.0868</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -4141,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>4917440000</v>
+        <v>4801160192</v>
       </c>
       <c r="BB2" t="n">
         <v>0.01114</v>
@@ -4153,13 +4434,13 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.44105</v>
+        <v>0.42745</v>
       </c>
       <c r="BF2" t="n">
         <v>24.073</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.0351846</v>
+        <v>0.98782873</v>
       </c>
       <c r="BH2" t="n">
         <v>1767139200</v>
@@ -4177,19 +4458,19 @@
         <v>60900000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.899</v>
+        <v>0.878</v>
       </c>
       <c r="BO2" t="n">
-        <v>12.982</v>
+        <v>12.675</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.2927928</v>
+        <v>-0.35190916</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="n">
         <v>0.29</v>
@@ -4203,7 +4484,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>24.92</v>
+        <v>23.78</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -4286,59 +4567,61 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CR2" t="n">
+        <v>1779969054</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>23.78</v>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
           <t>Jungheinrich AG</t>
         </is>
       </c>
-      <c r="CR2" t="b">
+      <c r="CU2" t="b">
         <v>0</v>
       </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CT2" t="n">
-        <v>1779969054</v>
-      </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>finmb_879453</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>Europe/Rome</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="CY2" t="n">
+      <c r="CZ2" t="n">
         <v>7200000</v>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>it_market</t>
         </is>
-      </c>
-      <c r="DA2" t="b">
-        <v>0</v>
       </c>
       <c r="DB2" t="b">
         <v>0</v>
       </c>
-      <c r="DC2" t="n">
-        <v>1748588400000</v>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="DD2" t="n">
-        <v>-1.0200005</v>
+        <v>-0.42000008</v>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
@@ -4354,10 +4637,10 @@
         <v>6</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.9400005299999999</v>
+        <v>-0.19999886</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.039199356</v>
+        <v>-0.008340235999999999</v>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
@@ -4365,28 +4648,28 @@
         </is>
       </c>
       <c r="DK2" t="n">
-        <v>-16.4</v>
+        <v>-17.539999</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0.39690223</v>
+        <v>-0.42449176</v>
       </c>
       <c r="DM2" t="n">
-        <v>-29.27928</v>
+        <v>-35.190918</v>
       </c>
       <c r="DN2" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="DO2" t="n">
-        <v>-4.451599</v>
+        <v>-3.6651993</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0.15156135</v>
+        <v>-0.1335461</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-6.695999</v>
+        <v>-7.306799</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.21179147</v>
+        <v>-0.23504508</v>
       </c>
       <c r="DS2" t="n">
         <v>20</v>
@@ -4394,16 +4677,14 @@
       <c r="DT2" t="n">
         <v>15</v>
       </c>
-      <c r="DU2" t="n">
-        <v>-3.9321527</v>
+      <c r="DU2" t="b">
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>1748588400000</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-1.7355375</v>
       </c>
       <c r="DX2" t="inlineStr"/>
     </row>
